--- a/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_P127_pos_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
+++ b/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_P127_pos_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5787172809428369</v>
+        <v>0.5553910027594239</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7839669903453134</v>
+        <v>0.8714354909638249</v>
       </c>
       <c r="C2" t="n">
-        <v>0.578717680992443</v>
+        <v>0.5553910027594239</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7839669903453134</v>
+        <v>0.8714354909638249</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4234765110873748</v>
+        <v>0.4384969319179846</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7125515522191569</v>
+        <v>0.8378040931671161</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9996491564954054</v>
+        <v>0.9994347757505652</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998526421199809</v>
+        <v>0.9998780386459163</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7469565217391304</v>
+        <v>0.8546086956521739</v>
       </c>
     </row>
   </sheetData>
